--- a/data/trans_dic/IP2003-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen dientes o muelas empastados</t>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 30,18</t>
+          <t>15,98; 30,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 28,31</t>
+          <t>14,32; 28,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 18,62</t>
+          <t>3,89; 16,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 34,83</t>
+          <t>5,48; 33,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 22,78</t>
+          <t>9,77; 22,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,14; 27,21</t>
+          <t>12,43; 27,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 27,48</t>
+          <t>11,44; 27,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 15,55</t>
+          <t>2,4; 17,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 24,44</t>
+          <t>14,81; 24,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,23; 25,69</t>
+          <t>15,49; 25,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 19,97</t>
+          <t>9,6; 20,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 21,97</t>
+          <t>5,01; 19,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 22,9</t>
+          <t>16,49; 22,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,87; 19,78</t>
+          <t>13,91; 19,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,98</t>
+          <t>12,42; 17,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 34,21</t>
+          <t>12,39; 33,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,14</t>
+          <t>11,68; 17,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,06</t>
+          <t>11,56; 16,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 15,58</t>
+          <t>10,55; 15,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 22,35</t>
+          <t>11,94; 22,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,86; 18,79</t>
+          <t>14,72; 18,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 17,52</t>
+          <t>13,31; 17,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,1; 15,96</t>
+          <t>12,05; 15,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 26,69</t>
+          <t>13,26; 24,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 14,82</t>
+          <t>6,57; 14,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 20,13</t>
+          <t>10,56; 20,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,6</t>
+          <t>7,49; 16,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 19,75</t>
+          <t>10,28; 20,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 18,3</t>
+          <t>9,44; 18,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 11,44</t>
+          <t>4,66; 11,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,93</t>
+          <t>7,38; 15,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,88</t>
+          <t>8,1; 17,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,86</t>
+          <t>8,95; 14,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 14,56</t>
+          <t>8,41; 14,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,3</t>
+          <t>8,31; 14,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 16,93</t>
+          <t>10,4; 16,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,19; 19,93</t>
+          <t>15,33; 20,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,21</t>
+          <t>14,54; 19,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,73</t>
+          <t>11,29; 15,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 29,11</t>
+          <t>12,76; 29,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,26</t>
+          <t>12,2; 16,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,47</t>
+          <t>11,29; 15,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,14</t>
+          <t>11,14; 15,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,73</t>
+          <t>11,39; 18,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 17,59</t>
+          <t>14,36; 17,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,43</t>
+          <t>13,33; 16,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,83</t>
+          <t>11,82; 14,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 21,63</t>
+          <t>12,89; 21,32</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18215</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5055</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7435</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15950</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12553</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>32811</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34166</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17608</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11895</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>14096; 27046</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12712; 25350</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2187; 9558</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2944; 17986</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8076; 18928</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10266; 22760</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7710; 18218</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1434; 10204</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>25307; 41748</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>26552; 44478</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11872; 24812</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5691; 21570</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69814</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66095</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83817</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65224</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59595</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>78881</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>142158</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>135327</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>125690</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>162698</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>65017; 89814</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58295; 83536</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54715; 78513</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56195; 149613</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>53106; 77757</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>53633; 76893</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>48918; 73754</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>60373; 113388</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>124981; 159059</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>117575; 153266</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>108915; 143334</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>127137; 236169</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>16549</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23202</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21796</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19322</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11333</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18753</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>22022</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>35871</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34535</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>36559</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>43818</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10676; 23257</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16370; 31202</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12130; 26417</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15161; 29723</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13843; 27025</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7276; 18330</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12521; 26386</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14754; 31746</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27678; 45885</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>26180; 45841</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27555; 46859</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>34270; 55487</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>113305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>111231</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88955</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>113048</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>105364</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>210840</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>204028</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>179856</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>218412</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>98898; 129850</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96409; 127193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74365; 103934</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83542; 192835</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>83435; 111397</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>79337; 107849</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>78067; 107974</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>85121; 138824</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>190813; 234248</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>182110; 225735</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>160639; 202155</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>180762; 298966</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2003-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,98; 30,66</t>
+          <t>15,68; 29,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 28,56</t>
+          <t>14,68; 27,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 16,99</t>
+          <t>3,86; 16,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 33,49</t>
+          <t>5,27; 32,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 22,89</t>
+          <t>9,88; 23,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 27,55</t>
+          <t>12,66; 27,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 27,04</t>
+          <t>11,22; 27,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 17,06</t>
+          <t>3,0; 16,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,81; 24,43</t>
+          <t>15,13; 24,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 25,95</t>
+          <t>15,55; 25,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 20,07</t>
+          <t>9,6; 20,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 19,0</t>
+          <t>5,65; 20,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 22,78</t>
+          <t>16,51; 23,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 19,94</t>
+          <t>13,56; 19,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,83</t>
+          <t>12,33; 18,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 33,0</t>
+          <t>12,35; 35,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 17,1</t>
+          <t>11,92; 17,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 16,57</t>
+          <t>11,45; 16,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,9</t>
+          <t>10,51; 15,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 22,43</t>
+          <t>11,85; 23,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 18,73</t>
+          <t>14,76; 18,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,35</t>
+          <t>13,35; 17,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 15,85</t>
+          <t>12,01; 15,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 24,63</t>
+          <t>13,38; 25,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 14,31</t>
+          <t>6,75; 14,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 20,12</t>
+          <t>10,77; 20,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 16,31</t>
+          <t>7,31; 15,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 20,15</t>
+          <t>10,32; 20,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 18,42</t>
+          <t>9,17; 18,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,75</t>
+          <t>3,79; 11,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,55</t>
+          <t>7,52; 15,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 17,44</t>
+          <t>8,13; 17,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,84</t>
+          <t>9,05; 14,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,73</t>
+          <t>8,42; 14,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 14,13</t>
+          <t>8,36; 14,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 16,83</t>
+          <t>9,9; 16,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 20,13</t>
+          <t>15,26; 20,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,19</t>
+          <t>14,58; 19,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,78</t>
+          <t>11,23; 15,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 29,46</t>
+          <t>12,89; 29,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,28</t>
+          <t>12,3; 16,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,35</t>
+          <t>11,25; 15,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,41</t>
+          <t>11,07; 15,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 18,57</t>
+          <t>11,3; 19,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,62</t>
+          <t>14,32; 17,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 16,53</t>
+          <t>13,44; 16,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 14,87</t>
+          <t>11,67; 14,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 21,32</t>
+          <t>12,77; 21,72</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14096; 27046</t>
+          <t>13828; 25840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12712; 25350</t>
+          <t>13030; 24694</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2187; 9558</t>
+          <t>2170; 9493</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2944; 17986</t>
+          <t>2832; 17396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8076; 18928</t>
+          <t>8173; 19390</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10266; 22760</t>
+          <t>10461; 22716</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7710; 18218</t>
+          <t>7562; 18309</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1434; 10204</t>
+          <t>1793; 10020</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25307; 41748</t>
+          <t>25858; 42051</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26552; 44478</t>
+          <t>26650; 43726</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11872; 24812</t>
+          <t>11871; 25238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5691; 21570</t>
+          <t>6416; 23803</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65017; 89814</t>
+          <t>65121; 91451</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58295; 83536</t>
+          <t>56828; 83310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54715; 78513</t>
+          <t>54300; 79457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56195; 149613</t>
+          <t>56008; 159620</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53106; 77757</t>
+          <t>54205; 78132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53633; 76893</t>
+          <t>53140; 78417</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48918; 73754</t>
+          <t>48727; 71610</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60373; 113388</t>
+          <t>59918; 119009</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>124981; 159059</t>
+          <t>125336; 159683</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117575; 153266</t>
+          <t>117916; 153460</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108915; 143334</t>
+          <t>108563; 142270</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>127137; 236169</t>
+          <t>128339; 246090</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10676; 23257</t>
+          <t>10975; 23530</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16370; 31202</t>
+          <t>16702; 31855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12130; 26417</t>
+          <t>11831; 24798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15161; 29723</t>
+          <t>15226; 29529</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13843; 27025</t>
+          <t>13446; 27201</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7276; 18330</t>
+          <t>5911; 17316</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12521; 26386</t>
+          <t>12771; 26085</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14754; 31746</t>
+          <t>14806; 32288</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27678; 45885</t>
+          <t>27978; 46064</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26180; 45841</t>
+          <t>26209; 44140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27555; 46859</t>
+          <t>27742; 47996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34270; 55487</t>
+          <t>32627; 54954</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98898; 129850</t>
+          <t>98461; 130729</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>96409; 127193</t>
+          <t>96632; 128679</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74365; 103934</t>
+          <t>73987; 105283</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83542; 192835</t>
+          <t>84360; 190087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83435; 111397</t>
+          <t>84137; 111514</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79337; 107849</t>
+          <t>79058; 108814</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78067; 107974</t>
+          <t>77560; 108202</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85121; 138824</t>
+          <t>84499; 142608</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190813; 234248</t>
+          <t>190408; 233928</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182110; 225735</t>
+          <t>183597; 225260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>160639; 202155</t>
+          <t>158663; 200926</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>180762; 298966</t>
+          <t>179041; 304557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2003-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>22,47%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20,52%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,98%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,63%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,68; 29,29</t>
+          <t>9,86; 22,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 27,82</t>
+          <t>13,14; 27,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 16,87</t>
+          <t>11,48; 27,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 32,4</t>
+          <t>2,26; 15,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 23,45</t>
+          <t>16,04; 30,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 27,49</t>
+          <t>13,69; 28,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 27,18</t>
+          <t>4,09; 18,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 16,76</t>
+          <t>4,25; 19,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 24,6</t>
+          <t>14,57; 24,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,55; 25,51</t>
+          <t>15,23; 25,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 20,41</t>
+          <t>9,69; 19,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 20,97</t>
+          <t>4,52; 14,04</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,51%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>16,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,19</t>
+          <t>11,83; 17,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 19,88</t>
+          <t>11,59; 17,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 18,04</t>
+          <t>10,26; 15,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 35,2</t>
+          <t>12,05; 21,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 17,18</t>
+          <t>16,52; 22,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 16,89</t>
+          <t>13,87; 19,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,44</t>
+          <t>12,06; 17,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 23,54</t>
+          <t>11,37; 17,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,76; 18,81</t>
+          <t>14,86; 18,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 17,38</t>
+          <t>13,27; 17,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 15,74</t>
+          <t>12,1; 15,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,66</t>
+          <t>12,77; 18,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,96%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,48</t>
+          <t>9,04; 18,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 20,54</t>
+          <t>4,3; 11,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 15,31</t>
+          <t>7,76; 15,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 20,01</t>
+          <t>7,48; 17,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 18,54</t>
+          <t>6,83; 14,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 11,1</t>
+          <t>10,31; 20,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 15,37</t>
+          <t>7,32; 15,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,73</t>
+          <t>10,03; 19,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,9</t>
+          <t>8,95; 14,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,19</t>
+          <t>8,35; 14,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,47</t>
+          <t>8,28; 14,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 16,67</t>
+          <t>10,08; 16,97</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,27</t>
+          <t>12,25; 16,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,41</t>
+          <t>11,39; 15,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,99</t>
+          <t>11,05; 15,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 29,04</t>
+          <t>11,22; 18,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 16,3</t>
+          <t>15,19; 19,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,48</t>
+          <t>14,38; 19,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,44</t>
+          <t>11,24; 15,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 19,08</t>
+          <t>11,83; 16,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 17,6</t>
+          <t>14,34; 17,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 16,49</t>
+          <t>13,25; 16,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 14,78</t>
+          <t>11,75; 14,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 21,72</t>
+          <t>12,2; 16,35</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15950</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12553</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>19822</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>18215</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5055</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7435</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12989</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15950</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12553</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>8283</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13828; 25840</t>
+          <t>8156; 18839</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13030; 24694</t>
+          <t>10859; 22478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2170; 9493</t>
+          <t>7736; 18515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2832; 17396</t>
+          <t>1243; 8511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8173; 19390</t>
+          <t>14146; 26623</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10461; 22716</t>
+          <t>12150; 25126</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7562; 18309</t>
+          <t>2303; 10476</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1793; 10020</t>
+          <t>1952; 8984</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25858; 42051</t>
+          <t>24899; 41773</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26650; 43726</t>
+          <t>26100; 44036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11871; 25238</t>
+          <t>11981; 24686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6416; 23803</t>
+          <t>4559; 14160</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65224</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59595</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71619</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>76934</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>69814</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>66095</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83817</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65224</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65513</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59595</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>60796</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>132415</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65121; 91451</t>
+          <t>53786; 77963</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56828; 83310</t>
+          <t>53783; 79178</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54300; 79457</t>
+          <t>47583; 72241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56008; 159620</t>
+          <t>56278; 100126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54205; 78132</t>
+          <t>65157; 90314</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53140; 78417</t>
+          <t>58101; 82885</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48727; 71610</t>
+          <t>53092; 79188</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59918; 119009</t>
+          <t>48466; 76089</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>125336; 159683</t>
+          <t>126166; 159564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117916; 153460</t>
+          <t>117181; 154697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108563; 142270</t>
+          <t>109427; 144312</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>128339; 246090</t>
+          <t>114037; 165220</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19322</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11333</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18753</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19647</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>16549</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>23202</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>17805</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21796</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19322</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11333</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18753</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>41792</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10975; 23530</t>
+          <t>13266; 26853</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16702; 31855</t>
+          <t>6710; 17852</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11831; 24798</t>
+          <t>13172; 27041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15226; 29529</t>
+          <t>12521; 28835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13446; 27201</t>
+          <t>11095; 24079</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5911; 17316</t>
+          <t>15987; 31215</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12771; 26085</t>
+          <t>11852; 25258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14806; 32288</t>
+          <t>14880; 29532</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27978; 46064</t>
+          <t>27686; 45944</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26209; 44140</t>
+          <t>25976; 45288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27742; 47996</t>
+          <t>27453; 47428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32627; 54954</t>
+          <t>31837; 53587</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98461; 130729</t>
+          <t>83791; 111239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>96632; 128679</t>
+          <t>80047; 108689</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73987; 105283</t>
+          <t>77447; 106142</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84360; 190087</t>
+          <t>77347; 124939</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84137; 111514</t>
+          <t>97996; 128552</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79058; 108814</t>
+          <t>95300; 127320</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77560; 108202</t>
+          <t>73998; 103586</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84499; 142608</t>
+          <t>73382; 104258</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190408; 233928</t>
+          <t>190612; 233777</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183597; 225260</t>
+          <t>180949; 224368</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>158663; 200926</t>
+          <t>159691; 201619</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>179041; 304557</t>
+          <t>159697; 214093</t>
         </is>
       </c>
     </row>
